--- a/data/gravel/Panorama Taiga 2025.xlsx
+++ b/data/gravel/Panorama Taiga 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F014CCC-FF34-0E47-B1BB-CE7690A228B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C524E6A3-E053-E041-B8A4-281621CE5090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32880" yWindow="-18480" windowWidth="24880" windowHeight="17660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -354,6 +354,9 @@
   </si>
   <si>
     <t>rigid carbon, 120 equiv at 20% sag</t>
+  </si>
+  <si>
+    <t>https://www.panoramacycles.com/cdn/shop/files/taiga-355781.jpg?v=1734450096</t>
   </si>
 </sst>
 </file>
@@ -361,7 +364,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -407,7 +410,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -750,6 +753,11 @@
         <v>96</v>
       </c>
     </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>107</v>
+      </c>
+    </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/Panorama Taiga 2025.xlsx
+++ b/data/gravel/Panorama Taiga 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C524E6A3-E053-E041-B8A4-281621CE5090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BCD3E0C-F8AE-A443-8D19-FAA5BE1C7B47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32880" yWindow="-18480" windowWidth="24880" windowHeight="17660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="110">
   <si>
     <t>brand</t>
   </si>
@@ -357,6 +357,12 @@
   </si>
   <si>
     <t>https://www.panoramacycles.com/cdn/shop/files/taiga-355781.jpg?v=1734450096</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Granby, Québec, Canada</t>
   </si>
 </sst>
 </file>
@@ -707,7 +713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1438,6 +1444,14 @@
         <v>102</v>
       </c>
     </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>108</v>
+      </c>
+      <c r="B73" t="s">
+        <v>109</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Panorama Taiga 2025.xlsx
+++ b/data/gravel/Panorama Taiga 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BCD3E0C-F8AE-A443-8D19-FAA5BE1C7B47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB439C7-A09D-0A49-A9EB-ACC9078B2D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -363,6 +363,24 @@
   </si>
   <si>
     <t>Granby, Québec, Canada</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -713,7 +731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1285,170 +1303,200 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>45</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
-      </c>
-      <c r="B51">
-        <v>31.6</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>48</v>
-      </c>
-      <c r="B52" s="1"/>
+        <v>113</v>
+      </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>45</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>53</v>
+        <v>47</v>
+      </c>
+      <c r="B57">
+        <v>31.6</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>54</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>103</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B58" s="1"/>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>55</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>104</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>56</v>
-      </c>
-      <c r="B60" s="1"/>
+        <v>50</v>
+      </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>58</v>
-      </c>
-      <c r="B62" s="1">
-        <v>1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>59</v>
-      </c>
-      <c r="B63" s="1">
-        <v>1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>60</v>
-      </c>
-      <c r="B64" s="1">
-        <v>1</v>
+        <v>54</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>61</v>
-      </c>
-      <c r="B65" s="1">
-        <v>3</v>
+        <v>55</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B66" s="1"/>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>63</v>
-      </c>
-      <c r="B67" s="1"/>
+        <v>57</v>
+      </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>64</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>70</v>
+        <v>58</v>
+      </c>
+      <c r="B68" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>59</v>
+      </c>
+      <c r="B69" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>60</v>
+      </c>
+      <c r="B70" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>61</v>
+      </c>
+      <c r="B71" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>62</v>
+      </c>
+      <c r="B72" s="1"/>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>63</v>
+      </c>
+      <c r="B73" s="1"/>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>64</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>65</v>
       </c>
-      <c r="B69">
+      <c r="B75">
         <f>949+434</f>
         <v>1383</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>66</v>
       </c>
-      <c r="B70">
+      <c r="B76">
         <v>2599</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>68</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>108</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>109</v>
       </c>
     </row>

--- a/data/gravel/Panorama Taiga 2025.xlsx
+++ b/data/gravel/Panorama Taiga 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB439C7-A09D-0A49-A9EB-ACC9078B2D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95588C85-9BEE-9A40-B090-BE5C80D932C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="118">
   <si>
     <t>brand</t>
   </si>
@@ -317,9 +317,6 @@
     <t>STEM LENGTH</t>
   </si>
   <si>
-    <t>a8:e32</t>
-  </si>
-  <si>
     <t>Taiga</t>
   </si>
   <si>
@@ -381,6 +378,15 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>a8:e34</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
   </si>
 </sst>
 </file>
@@ -731,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -750,7 +756,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -774,12 +780,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -787,7 +793,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1064,371 +1070,385 @@
         <v>500</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>23</v>
-      </c>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3"/>
+    </row>
+    <row r="26" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>26</v>
-      </c>
-      <c r="C28">
-        <v>700</v>
-      </c>
-      <c r="D28">
-        <v>700</v>
-      </c>
-      <c r="E28">
-        <v>700</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29">
-        <v>2.6</v>
-      </c>
-      <c r="D29">
-        <v>2.6</v>
-      </c>
-      <c r="E29">
-        <v>2.6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C30">
-        <v>2.8</v>
+        <v>700</v>
       </c>
       <c r="D30">
-        <v>2.8</v>
+        <v>700</v>
       </c>
       <c r="E30">
-        <v>2.8</v>
+        <v>700</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31">
+        <v>2.6</v>
+      </c>
+      <c r="D31">
+        <v>2.6</v>
+      </c>
+      <c r="E31">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32">
+        <v>2.8</v>
+      </c>
+      <c r="D32">
+        <v>2.8</v>
+      </c>
+      <c r="E32">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="4">
-        <f>C33*2.54</f>
+      <c r="C33" s="4">
+        <f>C35*2.54</f>
         <v>154.94</v>
       </c>
-      <c r="D31" s="4">
-        <f t="shared" ref="D31:E32" si="0">D33*2.54</f>
+      <c r="D33" s="4">
+        <f t="shared" ref="D33:E34" si="0">D35*2.54</f>
         <v>167.64000000000001</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E33" s="4">
         <f t="shared" si="0"/>
         <v>177.8</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>30</v>
       </c>
-      <c r="C32" s="4">
-        <f>C34*2.54</f>
+      <c r="C34" s="4">
+        <f>C36*2.54</f>
         <v>167.64000000000001</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D34" s="4">
         <f t="shared" si="0"/>
         <v>177.8</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E34" s="4">
         <f t="shared" si="0"/>
         <v>187.96</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C33">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C35">
         <v>61</v>
       </c>
-      <c r="D33">
+      <c r="D35">
         <v>66</v>
       </c>
-      <c r="E33">
+      <c r="E35">
         <v>70</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B34" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34">
-        <v>66</v>
-      </c>
-      <c r="D34">
-        <v>70</v>
-      </c>
-      <c r="E34">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>71</v>
-      </c>
-      <c r="B35" t="s">
-        <v>72</v>
-      </c>
-      <c r="C35" t="s">
-        <v>98</v>
-      </c>
-      <c r="D35" t="s">
-        <v>99</v>
-      </c>
-      <c r="E35" t="s">
-        <v>100</v>
-      </c>
-      <c r="F35" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>73</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>101</v>
+        <v>31</v>
+      </c>
+      <c r="B36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36">
+        <v>66</v>
+      </c>
+      <c r="D36">
+        <v>70</v>
+      </c>
+      <c r="E36">
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>74</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
+      </c>
+      <c r="B37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" t="s">
+        <v>97</v>
+      </c>
+      <c r="D37" t="s">
+        <v>98</v>
+      </c>
+      <c r="E37" t="s">
+        <v>99</v>
+      </c>
+      <c r="F37" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>33</v>
-      </c>
-      <c r="B38" t="s">
-        <v>34</v>
+        <v>73</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>36</v>
-      </c>
-      <c r="B40">
-        <v>20</v>
+        <v>33</v>
+      </c>
+      <c r="B40" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41">
-        <v>2.8</v>
+        <v>35</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42" s="1">
-        <v>3</v>
+        <v>36</v>
+      </c>
+      <c r="B42">
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B43">
-        <v>120</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>38</v>
+      </c>
+      <c r="B44" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="B45">
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>43</v>
-      </c>
-      <c r="B47">
-        <v>148</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>44</v>
-      </c>
-      <c r="B48">
-        <v>110</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>110</v>
+        <v>43</v>
+      </c>
+      <c r="B49">
+        <v>148</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>111</v>
+        <v>44</v>
+      </c>
+      <c r="B50">
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>45</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>46</v>
+        <v>114</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>47</v>
-      </c>
-      <c r="B57">
-        <v>31.6</v>
+        <v>45</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>48</v>
-      </c>
-      <c r="B58" s="1"/>
+        <v>46</v>
+      </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>49</v>
+        <v>47</v>
+      </c>
+      <c r="B59">
+        <v>31.6</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>50</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B60" s="1"/>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>54</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>103</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>55</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>56</v>
-      </c>
-      <c r="B66" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>57</v>
+        <v>55</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>58</v>
-      </c>
-      <c r="B68" s="1">
-        <v>1</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B68" s="1"/>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>59</v>
-      </c>
-      <c r="B69" s="1">
-        <v>1</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B70" s="1">
         <v>1</v>
@@ -1436,68 +1456,84 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B71" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>62</v>
-      </c>
-      <c r="B72" s="1"/>
+        <v>60</v>
+      </c>
+      <c r="B72" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>63</v>
-      </c>
-      <c r="B73" s="1"/>
+        <v>61</v>
+      </c>
+      <c r="B73" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>64</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>70</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B74" s="1"/>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75" s="1"/>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>64</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>65</v>
       </c>
-      <c r="B75">
+      <c r="B77">
         <f>949+434</f>
         <v>1383</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>66</v>
-      </c>
-      <c r="B76">
-        <v>2599</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>67</v>
-      </c>
-    </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>68</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>102</v>
+        <v>66</v>
+      </c>
+      <c r="B78">
+        <v>2599</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>68</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>107</v>
+      </c>
+      <c r="B81" t="s">
         <v>108</v>
-      </c>
-      <c r="B79" t="s">
-        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Panorama Taiga 2025.xlsx
+++ b/data/gravel/Panorama Taiga 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95588C85-9BEE-9A40-B090-BE5C80D932C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5714512A-6A94-DD46-9721-FA57D7897565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
